--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1699.22</v>
+        <v>1681.43</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1219.89</v>
+        <v>1207.12</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3020.36</v>
+        <v>3016.51</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7486.83</v>
+        <v>7473.55</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>943.78</v>
+        <v>931.79</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2149.93</v>
+        <v>2122.62</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4222.94</v>
+        <v>4169.3</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2552.58</v>
+        <v>2527.19</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20854.38</v>
+        <v>20646.89</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4218.68</v>
+        <v>4203.56</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1619.23</v>
+        <v>1626.57</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1321.02</v>
+        <v>1327.01</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1244.84</v>
+        <v>1246.43</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3269.8</v>
+        <v>3273.99</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>969.5</v>
+        <v>977.78</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3712.02</v>
+        <v>3751.84</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>893.45</v>
+        <v>898.33</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5412.69</v>
+        <v>5442.29</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2322.08</v>
+        <v>2292.07</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3827.14</v>
+        <v>3819.6</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6839.27</v>
+        <v>6834.59</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9650.540000000001</v>
+        <v>9713.790000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1128.17</v>
+        <v>1143.37</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4900.2</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2247.51</v>
+        <v>2302.17</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2844.79</v>
+        <v>2931.05</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1658.66</v>
+        <v>1707.96</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>880.55</v>
+        <v>906.73</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>938.53</v>
+        <v>966.42</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1948.52</v>
+        <v>1954.16</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2505.57</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>946.8099999999999</v>
+        <v>942.8200000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4684</v>
+        <v>4696.86</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5374.89</v>
+        <v>5410.29</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8258.82</v>
+        <v>8199.66</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>846.51</v>
+        <v>840.45</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10792.18</v>
+        <v>10776.3</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5241.37</v>
+        <v>5212.83</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>864.63</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1679.77</v>
+        <v>1681.39</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1353.29</v>
+        <v>1354.46</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2125.41</v>
+        <v>2134.18</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2508.38</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1414.01</v>
+        <v>1392.92</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4517.82</v>
+        <v>4452.46</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>833.41</v>
+        <v>835.84</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>821.8</v>
+        <v>831.91</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1380.77</v>
+        <v>1399.16</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1183.54</v>
+        <v>1199.29</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>929.3200000000001</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>793.29</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>798.9400000000001</v>
+        <v>809.5700000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2545.7</v>
+        <v>2578.92</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1330.78</v>
+        <v>1363.53</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1526.19</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4615.74</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3261.83</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12920.58</v>
+        <v>12974.14</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1112.44</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4714.73</v>
+        <v>4759.53</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1155.29</v>
+        <v>1142.73</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>788.85</v>
+        <v>786.9</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1166.15</v>
+        <v>1171.88</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4512.39</v>
+        <v>4526.75</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1046.58</v>
+        <v>1052.14</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2181.16</v>
+        <v>2206.74</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2531.17</v>
+        <v>2560.86</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5402.59</v>
+        <v>5453.27</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>873.98</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>808.14</v>
+        <v>803.13</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1008.82</v>
+        <v>1011.94</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>912.13</v>
+        <v>914.95</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4288.33</v>
+        <v>4231.21</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16138.36</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>977.0599999999999</v>
+        <v>957.9299999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4445.72</v>
+        <v>4379.85</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>813.54</v>
+        <v>821.72</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>818.21</v>
+        <v>820.08</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>848.8</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2888.05</v>
+        <v>2907.38</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3035.16</v>
+        <v>3055.48</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1798.39</v>
+        <v>1810.43</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1132.74</v>
+        <v>1140.67</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>770.21</v>
+        <v>768.67</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1398.54</v>
+        <v>1390.44</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2482.4</v>
+        <v>2468.03</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,129 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1589.65</v>
+        <v>1564.16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3950-1230-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1278.05</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3949-338-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>1807.67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2713-1114-CM25</t>
+          <t>1079689-254-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1681.43</v>
+        <v>17525.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057062-645-CM25</t>
+          <t>1233615-1316-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1207.12</v>
+        <v>5620.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1233615-11767-CM25</t>
+          <t>3950-4268-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3016.51</v>
+        <v>1067.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>868-323-CM25</t>
+          <t>886182-234-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7473.55</v>
+        <v>2530.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3949-424-CM25</t>
+          <t>1692-2857-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>931.79</v>
+        <v>759.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3949-425-CM25</t>
+          <t>3950-4623-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2122.62</v>
+        <v>1465.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3950-4822-CM25</t>
+          <t>1057062-645-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4169.3</v>
+        <v>1207.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>854-384-CM25</t>
+          <t>2713-1114-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2527.19</v>
+        <v>1681.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>854-385-CM25</t>
+          <t>1233615-11767-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20646.89</v>
+        <v>3016.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3950-4846-CM25</t>
+          <t>868-323-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4203.56</v>
+        <v>7473.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2713-1298-CM25</t>
+          <t>3949-424-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1626.57</v>
+        <v>931.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>854-405-CM25</t>
+          <t>3949-425-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1327.01</v>
+        <v>2122.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1692-3032-CM25</t>
+          <t>3950-4822-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1246.43</v>
+        <v>4169.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>742-218-CM25</t>
+          <t>854-384-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3273.99</v>
+        <v>2527.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2713-1330-CM25</t>
+          <t>854-385-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>977.78</v>
+        <v>20646.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3949-476-CM25</t>
+          <t>3950-4846-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3751.84</v>
+        <v>4203.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1078218-31-CM25</t>
+          <t>2713-1298-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>898.33</v>
+        <v>1626.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3949-481-CM25</t>
+          <t>854-405-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5442.29</v>
+        <v>1327.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2713-21-CM26</t>
+          <t>1692-3032-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2292.07</v>
+        <v>1246.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3171-1-CM26</t>
+          <t>742-218-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.102.094-5</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3819.6</v>
+        <v>3273.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1691-3673-CM25</t>
+          <t>2713-1330-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6834.59</v>
+        <v>977.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>707426-4-CM26</t>
+          <t>3949-476-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9713.790000000001</v>
+        <v>3751.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1003-5-CM26</t>
+          <t>1078218-31-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1143.37</v>
+        <v>898.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2713-90-CM26</t>
+          <t>3949-481-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5019.36</v>
+        <v>5442.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3791-52-CM26</t>
+          <t>2713-21-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2302.17</v>
+        <v>2292.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3950-108-CM26</t>
+          <t>3171-1-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>GOBERNACION MARITIMA DE AYSEN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2931.05</v>
+        <v>3819.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3622-7-CM26</t>
+          <t>1691-3673-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1707.96</v>
+        <v>6834.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3622-8-CM26</t>
+          <t>707426-4-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>906.73</v>
+        <v>9713.790000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3622-10-CM26</t>
+          <t>1003-5-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>966.42</v>
+        <v>1143.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>951405-26-CM26</t>
+          <t>2713-90-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1954.16</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1691-210-CM26</t>
+          <t>3791-52-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2495</v>
+        <v>2302.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1692-76-CM26</t>
+          <t>3950-108-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>942.8200000000001</v>
+        <v>2931.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2713-172-CM26</t>
+          <t>3622-7-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4696.86</v>
+        <v>1707.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4054-4-CM26</t>
+          <t>3622-8-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5410.29</v>
+        <v>906.73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>886182-45-CM26</t>
+          <t>3622-10-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8199.66</v>
+        <v>966.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3797-120-CM26</t>
+          <t>951405-26-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>840.45</v>
+        <v>1954.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>951405-25-CM26</t>
+          <t>1692-76-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10776.3</v>
+        <v>942.8200000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>734-57-CM26</t>
+          <t>1691-210-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5212.83</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2713-248-CM26</t>
+          <t>2713-172-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>861.3</v>
+        <v>4696.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1428-15-CM26</t>
+          <t>4054-4-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1681.39</v>
+        <v>5410.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4626-6-CM26</t>
+          <t>886182-45-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1354.46</v>
+        <v>8199.66</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>854-33-CM26</t>
+          <t>3797-120-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2134.18</v>
+        <v>840.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>854-34-CM26</t>
+          <t>951405-25-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2518.75</v>
+        <v>10776.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2713-331-CM26</t>
+          <t>734-57-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1392.92</v>
+        <v>5212.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1274667-128-CM26</t>
+          <t>2713-248-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4452.46</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1403-238-CM26</t>
+          <t>1428-15-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>835.84</v>
+        <v>1681.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2500-57-CM26</t>
+          <t>4626-6-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>831.91</v>
+        <v>1354.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2500-62-CM26</t>
+          <t>854-34-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1399.16</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2500-63-CM26</t>
+          <t>854-33-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1199.29</v>
+        <v>2134.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2500-64-CM26</t>
+          <t>2713-331-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>941.7</v>
+        <v>1392.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2500-66-CM26</t>
+          <t>1274667-128-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>803.85</v>
+        <v>4452.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2500-67-CM26</t>
+          <t>1403-238-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ARTEL S.A.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>92.642.000-3</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>809.5700000000001</v>
+        <v>835.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2151-128-CM26</t>
+          <t>2500-57-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2578.92</v>
+        <v>831.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4626-12-CM26</t>
+          <t>2500-62-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1363.53</v>
+        <v>1399.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1274667-151-CM26</t>
+          <t>2500-63-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1555.05</v>
+        <v>1199.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2500-59-CM26</t>
+          <t>2500-64-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4703.04</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2500-61-CM26</t>
+          <t>2500-66-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3323.52</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4778-237-CM26</t>
+          <t>2500-67-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ARTEL S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>92.642.000-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12974.14</v>
+        <v>809.5700000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1426103-37-CM26</t>
+          <t>2151-128-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1116.65</v>
+        <v>2578.92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079689-187-CM26</t>
+          <t>4626-12-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4759.53</v>
+        <v>1363.53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3950-726-CM26</t>
+          <t>1274667-151-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1142.73</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3950-728-CM26</t>
+          <t>2500-59-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>786.9</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1692-353-CM26</t>
+          <t>2500-61-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1171.88</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4778-306-CM26</t>
+          <t>4778-237-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4526.75</v>
+        <v>12974.14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3797-388-CM26</t>
+          <t>1426103-37-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1052.14</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2713-598-CM26</t>
+          <t>1079689-187-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2206.74</v>
+        <v>4759.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4778-325-CM26</t>
+          <t>3950-726-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2560.86</v>
+        <v>1142.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1079689-229-CM26</t>
+          <t>3950-728-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5453.27</v>
+        <v>786.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1403-429-CM26</t>
+          <t>1692-353-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>861.97</v>
+        <v>1171.88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1256-5-CM26</t>
+          <t>4778-306-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.805.025-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>803.13</v>
+        <v>4526.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>749-15-CM26</t>
+          <t>3797-388-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1011.94</v>
+        <v>1052.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>749-16-CM26</t>
+          <t>2713-598-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>914.95</v>
+        <v>2206.74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>854-114-CM26</t>
+          <t>4778-325-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4231.21</v>
+        <v>2560.86</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>854-117-CM26</t>
+          <t>1079689-229-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>15923.39</v>
+        <v>5453.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1078461-8-CM26</t>
+          <t>1403-429-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>957.9299999999999</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1426103-58-CM26</t>
+          <t>1256-5-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.805.025-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Tesorería Regional de Aysén</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4379.85</v>
+        <v>803.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3950-925-CM26</t>
+          <t>749-15-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>821.72</v>
+        <v>1011.94</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1079689-291-CM26</t>
+          <t>749-16-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,27 +5221,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>820.08</v>
+        <v>914.95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1274667-255-CM26</t>
+          <t>854-114-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>854.48</v>
+        <v>4231.21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1274667-259-CM26</t>
+          <t>854-117-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,27 +5343,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2907.38</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>734-485-CM26</t>
+          <t>1078461-8-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3055.48</v>
+        <v>957.9299999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>734-486-CM26</t>
+          <t>1426103-58-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1810.43</v>
+        <v>4379.85</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4778-404-CM26</t>
+          <t>3950-925-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1140.67</v>
+        <v>821.72</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5019-182-CM26</t>
+          <t>1079689-291-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>768.67</v>
+        <v>820.08</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>967384-2-CM26</t>
+          <t>1274667-255-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1390.44</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>951405-275-CM26</t>
+          <t>1274667-259-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2468.03</v>
+        <v>2907.38</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2713-806-CM26</t>
+          <t>734-485-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1564.16</v>
+        <v>3055.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3950-1230-CM26</t>
+          <t>734-486-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,27 +5831,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1278.05</v>
+        <v>1810.43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3949-338-CM26</t>
+          <t>4778-404-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,6 +5937,372 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
+        <v>1140.67</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>5019-182-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>768.67</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>967384-2-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.999.100-1</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ejército de Chile</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>1390.44</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>951405-275-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2468.03</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2713-806-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>1564.16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3950-1230-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1278.05</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3949-338-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
         <v>1807.67</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079689-254-CM25</t>
+          <t>3950-3939-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17525.46</v>
+        <v>795.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233615-1316-CM25</t>
+          <t>2713-635-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5620.79</v>
+        <v>1684.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3950-4268-CM25</t>
+          <t>2713-634-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1067.53</v>
+        <v>3616.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>886182-234-CM25</t>
+          <t>951405-242-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2530.89</v>
+        <v>3773.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1692-2857-CM25</t>
+          <t>1003-154-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>759.17</v>
+        <v>1027.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3950-4623-CM25</t>
+          <t>1079689-254-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1465.36</v>
+        <v>17525.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057062-645-CM25</t>
+          <t>1252675-67-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1207.12</v>
+        <v>923.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2713-1114-CM25</t>
+          <t>1233615-1316-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1681.43</v>
+        <v>5620.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233615-11767-CM25</t>
+          <t>951405-287-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3016.51</v>
+        <v>1855.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>868-323-CM25</t>
+          <t>2713-824-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7473.55</v>
+        <v>2064.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3949-424-CM25</t>
+          <t>3950-4268-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>931.79</v>
+        <v>1067.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3949-425-CM25</t>
+          <t>1691-2345-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2122.62</v>
+        <v>8149.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3950-4822-CM25</t>
+          <t>734-898-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4169.3</v>
+        <v>3177.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>854-384-CM25</t>
+          <t>1746-228-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2527.19</v>
+        <v>953</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>854-385-CM25</t>
+          <t>886182-234-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20646.89</v>
+        <v>2530.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3950-4846-CM25</t>
+          <t>707426-159-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4203.56</v>
+        <v>2491.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2713-1298-CM25</t>
+          <t>2151-354-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1626.57</v>
+        <v>1215.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>854-405-CM25</t>
+          <t>1692-2857-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1327.01</v>
+        <v>759.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1692-3032-CM25</t>
+          <t>854-332-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1246.43</v>
+        <v>1452.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>742-218-CM25</t>
+          <t>3950-4623-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3273.99</v>
+        <v>1465.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2713-1330-CM25</t>
+          <t>2713-1114-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>977.78</v>
+        <v>1681.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3949-476-CM25</t>
+          <t>1057062-645-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3751.84</v>
+        <v>1207.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1078218-31-CM25</t>
+          <t>1233615-11767-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>898.33</v>
+        <v>3016.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3949-481-CM25</t>
+          <t>868-323-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5442.29</v>
+        <v>7473.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2713-21-CM26</t>
+          <t>3950-4822-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2292.07</v>
+        <v>4169.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3171-1-CM26</t>
+          <t>3949-425-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.102.094-5</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3819.6</v>
+        <v>2122.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1691-3673-CM25</t>
+          <t>3949-424-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6834.59</v>
+        <v>931.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>707426-4-CM26</t>
+          <t>854-385-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9713.790000000001</v>
+        <v>20646.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1003-5-CM26</t>
+          <t>854-384-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1143.37</v>
+        <v>2527.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2713-90-CM26</t>
+          <t>3950-4846-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5019.36</v>
+        <v>4203.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3791-52-CM26</t>
+          <t>2713-1298-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2302.17</v>
+        <v>1626.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3950-108-CM26</t>
+          <t>854-405-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2931.05</v>
+        <v>1327.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3622-7-CM26</t>
+          <t>742-218-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1707.96</v>
+        <v>3273.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3622-8-CM26</t>
+          <t>1692-3032-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>906.73</v>
+        <v>1246.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3622-10-CM26</t>
+          <t>2713-1330-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>966.42</v>
+        <v>977.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>951405-26-CM26</t>
+          <t>3949-476-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1954.16</v>
+        <v>3751.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1692-76-CM26</t>
+          <t>1078218-31-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>942.8200000000001</v>
+        <v>898.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1691-210-CM26</t>
+          <t>3949-481-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2495</v>
+        <v>5442.29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2713-172-CM26</t>
+          <t>2713-21-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4696.86</v>
+        <v>2292.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4054-4-CM26</t>
+          <t>3171-1-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>GOBERNACION MARITIMA DE AYSEN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5410.29</v>
+        <v>3819.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>886182-45-CM26</t>
+          <t>1691-3673-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8199.66</v>
+        <v>6834.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3797-120-CM26</t>
+          <t>707426-4-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>840.45</v>
+        <v>9713.790000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>951405-25-CM26</t>
+          <t>1003-5-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10776.3</v>
+        <v>1143.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>734-57-CM26</t>
+          <t>3791-52-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5212.83</v>
+        <v>2302.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2713-248-CM26</t>
+          <t>2713-90-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>861.3</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1428-15-CM26</t>
+          <t>3950-108-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1681.39</v>
+        <v>2931.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4626-6-CM26</t>
+          <t>3622-7-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1354.46</v>
+        <v>1707.96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>854-34-CM26</t>
+          <t>3622-8-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2518.75</v>
+        <v>906.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>854-33-CM26</t>
+          <t>3622-10-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2134.18</v>
+        <v>966.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2713-331-CM26</t>
+          <t>951405-26-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1392.92</v>
+        <v>1954.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1274667-128-CM26</t>
+          <t>1691-210-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4452.46</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1403-238-CM26</t>
+          <t>1692-76-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>835.84</v>
+        <v>942.8200000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2500-57-CM26</t>
+          <t>2713-172-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>831.91</v>
+        <v>4696.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2500-62-CM26</t>
+          <t>4054-4-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1399.16</v>
+        <v>5410.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2500-63-CM26</t>
+          <t>886182-45-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1199.29</v>
+        <v>8199.66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2500-64-CM26</t>
+          <t>3797-120-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>941.7</v>
+        <v>840.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2500-66-CM26</t>
+          <t>951405-25-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>803.85</v>
+        <v>10776.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2500-67-CM26</t>
+          <t>734-57-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ARTEL S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>92.642.000-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>809.5700000000001</v>
+        <v>5212.83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2151-128-CM26</t>
+          <t>2713-248-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2578.92</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4626-12-CM26</t>
+          <t>1428-15-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1363.53</v>
+        <v>1681.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1274667-151-CM26</t>
+          <t>4626-6-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1555.05</v>
+        <v>1354.46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2500-59-CM26</t>
+          <t>854-33-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4703.04</v>
+        <v>2134.18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2500-61-CM26</t>
+          <t>854-34-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3323.52</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4778-237-CM26</t>
+          <t>2713-331-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12974.14</v>
+        <v>1392.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1426103-37-CM26</t>
+          <t>1274667-128-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1116.65</v>
+        <v>4452.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1079689-187-CM26</t>
+          <t>1403-238-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4759.53</v>
+        <v>835.84</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3950-726-CM26</t>
+          <t>2500-57-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1142.73</v>
+        <v>831.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3950-728-CM26</t>
+          <t>2500-62-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>786.9</v>
+        <v>1399.16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1692-353-CM26</t>
+          <t>2500-63-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1171.88</v>
+        <v>1199.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4778-306-CM26</t>
+          <t>2500-64-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4526.75</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3797-388-CM26</t>
+          <t>2500-66-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1052.14</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2713-598-CM26</t>
+          <t>2500-67-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>ARTEL S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>92.642.000-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2206.74</v>
+        <v>809.5700000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4778-325-CM26</t>
+          <t>2151-128-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2560.86</v>
+        <v>2578.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1079689-229-CM26</t>
+          <t>4626-12-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,27 +4977,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5453.27</v>
+        <v>1363.53</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1403-429-CM26</t>
+          <t>2500-59-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>861.97</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1256-5-CM26</t>
+          <t>2500-61-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.805.025-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>803.13</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>749-15-CM26</t>
+          <t>1274667-151-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1011.94</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>749-16-CM26</t>
+          <t>4778-237-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>914.95</v>
+        <v>12974.14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>854-114-CM26</t>
+          <t>1426103-37-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,27 +5282,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4231.21</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>854-117-CM26</t>
+          <t>1079689-187-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,27 +5343,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>15923.39</v>
+        <v>4759.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1078461-8-CM26</t>
+          <t>3950-726-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>957.9299999999999</v>
+        <v>1142.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1426103-58-CM26</t>
+          <t>3950-728-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4379.85</v>
+        <v>786.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3950-925-CM26</t>
+          <t>1692-353-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>821.72</v>
+        <v>1171.88</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1079689-291-CM26</t>
+          <t>4778-306-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>820.08</v>
+        <v>4526.75</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1274667-255-CM26</t>
+          <t>3797-388-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>854.48</v>
+        <v>1052.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1274667-259-CM26</t>
+          <t>4778-325-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2907.38</v>
+        <v>2560.86</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>734-485-CM26</t>
+          <t>2713-598-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3055.48</v>
+        <v>2206.74</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>734-486-CM26</t>
+          <t>1079689-229-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1810.43</v>
+        <v>5453.27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4778-404-CM26</t>
+          <t>1403-429-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1140.67</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5019-182-CM26</t>
+          <t>1256-5-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>60.805.025-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Tesorería Regional de Aysén</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>768.67</v>
+        <v>803.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>967384-2-CM26</t>
+          <t>749-15-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1390.44</v>
+        <v>1011.94</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>951405-275-CM26</t>
+          <t>749-16-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2468.03</v>
+        <v>914.95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2713-806-CM26</t>
+          <t>854-114-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,27 +6136,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1564.16</v>
+        <v>4231.21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3950-1230-CM26</t>
+          <t>854-117-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1278.05</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3949-338-CM26</t>
+          <t>1078461-8-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,7 +6303,1349 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
+        <v>957.9299999999999</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1426103-58-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>4379.85</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3950-925-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>821.72</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1079689-291-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>820.08</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1274667-255-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>854.48</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1274667-259-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>2907.38</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>734-485-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>3055.48</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>734-486-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1810.43</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4778-404-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>1140.67</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>5019-182-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>768.67</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>967384-2-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.999.100-1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ejército de Chile</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>1390.44</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>951405-275-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>2468.03</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2713-806-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>1564.16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3950-1230-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1278.05</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>707426-115-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>2427.43</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2151-314-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.955.038-0</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>844.95</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3949-338-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
         <v>1807.67</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1692-563-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>1182.38</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2500-127-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>807.59</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2500-126-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>3960.16</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2500-129-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1652.06</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3951-231-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.974.700-3</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>8074.89</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>886182-275-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>7443.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>707426-159-CM25</t>
+          <t>2151-354-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2491.6</v>
+        <v>1215.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2151-354-CM25</t>
+          <t>707426-159-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1215.93</v>
+        <v>2491.6</v>
       </c>
     </row>
     <row r="19">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1003-5-CM26</t>
+          <t>2713-90-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1143.37</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="45">
@@ -3198,7 +3198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2713-90-CM26</t>
+          <t>3950-108-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5019.36</v>
+        <v>2931.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3950-108-CM26</t>
+          <t>3622-10-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2931.05</v>
+        <v>966.42</v>
       </c>
     </row>
     <row r="48">
@@ -3442,7 +3442,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3622-10-CM26</t>
+          <t>951405-26-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>966.42</v>
+        <v>1954.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>951405-26-CM26</t>
+          <t>1691-210-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1954.16</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1691-210-CM26</t>
+          <t>1692-76-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2495</v>
+        <v>942.8200000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1692-76-CM26</t>
+          <t>2713-172-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>942.8200000000001</v>
+        <v>4696.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2713-172-CM26</t>
+          <t>4054-4-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4696.86</v>
+        <v>5410.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4054-4-CM26</t>
+          <t>886182-45-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5410.29</v>
+        <v>8199.66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>886182-45-CM26</t>
+          <t>3797-120-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8199.66</v>
+        <v>840.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3797-120-CM26</t>
+          <t>951405-25-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>840.45</v>
+        <v>10776.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>951405-25-CM26</t>
+          <t>734-57-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>10776.3</v>
+        <v>5212.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>734-57-CM26</t>
+          <t>2713-248-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5212.83</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2713-248-CM26</t>
+          <t>1428-15-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>861.3</v>
+        <v>1681.39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1428-15-CM26</t>
+          <t>4626-6-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1681.39</v>
+        <v>1354.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4626-6-CM26</t>
+          <t>854-34-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1354.46</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="63">
@@ -4296,7 +4296,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>854-34-CM26</t>
+          <t>2713-331-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2518.75</v>
+        <v>1392.92</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2713-331-CM26</t>
+          <t>1274667-128-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1392.92</v>
+        <v>4452.46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1274667-128-CM26</t>
+          <t>1403-238-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4452.46</v>
+        <v>835.84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1403-238-CM26</t>
+          <t>2500-57-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>835.84</v>
+        <v>831.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2500-57-CM26</t>
+          <t>2500-62-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>831.91</v>
+        <v>1399.16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2500-62-CM26</t>
+          <t>2500-63-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1399.16</v>
+        <v>1199.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2500-63-CM26</t>
+          <t>2500-64-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1199.29</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2500-64-CM26</t>
+          <t>2500-66-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>941.7</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2500-66-CM26</t>
+          <t>2500-67-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>ARTEL S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
+          <t>92.642.000-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>803.85</v>
+        <v>809.5700000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2500-67-CM26</t>
+          <t>2151-128-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ARTEL S.A.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>92.642.000-3</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>809.5700000000001</v>
+        <v>2578.92</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2151-128-CM26</t>
+          <t>4626-12-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2578.92</v>
+        <v>1363.53</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4626-12-CM26</t>
+          <t>2500-59-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1363.53</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2500-59-CM26</t>
+          <t>2500-61-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4703.04</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2500-61-CM26</t>
+          <t>1274667-151-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3323.52</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1274667-151-CM26</t>
+          <t>4778-237-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1555.05</v>
+        <v>12974.14</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4778-237-CM26</t>
+          <t>1426103-37-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>12974.14</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1426103-37-CM26</t>
+          <t>1079689-187-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1116.65</v>
+        <v>4759.53</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1079689-187-CM26</t>
+          <t>3950-726-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4759.53</v>
+        <v>1142.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3950-726-CM26</t>
+          <t>3950-728-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1142.73</v>
+        <v>786.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3950-728-CM26</t>
+          <t>1692-353-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>786.9</v>
+        <v>1171.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1692-353-CM26</t>
+          <t>4778-306-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1171.88</v>
+        <v>4526.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4778-306-CM26</t>
+          <t>3797-388-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4526.75</v>
+        <v>1052.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3797-388-CM26</t>
+          <t>4778-325-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1052.14</v>
+        <v>2560.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4778-325-CM26</t>
+          <t>2713-598-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2560.86</v>
+        <v>2206.74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2713-598-CM26</t>
+          <t>1079689-229-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2206.74</v>
+        <v>5453.27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1079689-229-CM26</t>
+          <t>1403-429-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5453.27</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1403-429-CM26</t>
+          <t>1256-5-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>60.805.025-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>861.97</v>
+        <v>803.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1256-5-CM26</t>
+          <t>749-15-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>60.805.025-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>803.13</v>
+        <v>1011.94</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>749-15-CM26</t>
+          <t>749-16-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1011.94</v>
+        <v>914.95</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>749-16-CM26</t>
+          <t>854-117-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>914.95</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="94">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6187,7 +6187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>854-117-CM26</t>
+          <t>1078461-8-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>15923.39</v>
+        <v>957.9299999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1078461-8-CM26</t>
+          <t>1426103-58-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>957.9299999999999</v>
+        <v>4379.85</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1426103-58-CM26</t>
+          <t>3950-925-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4379.85</v>
+        <v>821.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3950-925-CM26</t>
+          <t>1079689-291-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>821.72</v>
+        <v>820.08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1079689-291-CM26</t>
+          <t>1274667-255-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>820.08</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1274667-255-CM26</t>
+          <t>1274667-259-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>854.48</v>
+        <v>2907.38</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1274667-259-CM26</t>
+          <t>734-485-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2907.38</v>
+        <v>3055.48</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>734-485-CM26</t>
+          <t>734-486-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3055.48</v>
+        <v>1810.43</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>734-486-CM26</t>
+          <t>4778-404-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1810.43</v>
+        <v>1140.67</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4778-404-CM26</t>
+          <t>5019-182-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1140.67</v>
+        <v>768.67</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5019-182-CM26</t>
+          <t>967384-2-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>61.999.100-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>768.67</v>
+        <v>1390.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>967384-2-CM26</t>
+          <t>951405-275-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,17 +6878,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1390.44</v>
+        <v>2468.03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>951405-275-CM26</t>
+          <t>2713-806-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2468.03</v>
+        <v>1564.16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2713-806-CM26</t>
+          <t>3950-1230-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1564.16</v>
+        <v>1278.05</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3950-1230-CM26</t>
+          <t>707426-115-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1278.05</v>
+        <v>2427.43</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>707426-115-CM26</t>
+          <t>2151-314-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.955.038-0</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2427.43</v>
+        <v>844.95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2151-314-CM26</t>
+          <t>3949-338-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>844.95</v>
+        <v>1807.67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3949-338-CM26</t>
+          <t>1692-563-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1807.67</v>
+        <v>1182.38</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1692-563-CM26</t>
+          <t>2500-127-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1182.38</v>
+        <v>807.59</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2500-127-CM26</t>
+          <t>2500-126-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>807.59</v>
+        <v>3960.16</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2500-126-CM26</t>
+          <t>2500-129-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3960.16</v>
+        <v>1652.06</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2500-129-CM26</t>
+          <t>3951-231-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1652.06</v>
+        <v>8074.89</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3951-231-CM26</t>
+          <t>886182-275-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,17 +7549,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8074.89</v>
+        <v>7443.42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>886182-275-CM26</t>
+          <t>418-2950-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7600,27 +7600,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,7 +7645,251 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7443.42</v>
+        <v>3802.74</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3949-369-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>1556.47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2713-1016-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>1651.15</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4778-608-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>5027.31</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>742-92-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>RED OFFICE SUR LTDA.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>800.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1538,7 +1538,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1426103-30-CM25</t>
+          <t>3171-29-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1239.8</v>
+        <v>3975.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3171-29-CM25</t>
+          <t>1426103-30-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.102.094-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3975.74</v>
+        <v>1239.8</v>
       </c>
     </row>
     <row r="20">
@@ -2054,7 +2054,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3949-107-CM25</t>
+          <t>1686-3-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1175.25</v>
+        <v>1076.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1686-3-CM25</t>
+          <t>3949-107-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1076.77</v>
+        <v>1175.25</v>
       </c>
     </row>
     <row r="28">
@@ -3277,7 +3277,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2713-635-CM25</t>
+          <t>2713-634-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1684.96</v>
+        <v>3616.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2713-634-CM25</t>
+          <t>2713-635-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3616.42</v>
+        <v>1684.96</v>
       </c>
     </row>
     <row r="47">
@@ -3521,7 +3521,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1079689-254-CM25</t>
+          <t>1252675-67-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>17525.46</v>
+        <v>923.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1252675-67-CM25</t>
+          <t>1079689-254-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>923.2</v>
+        <v>17525.46</v>
       </c>
     </row>
     <row r="51">
@@ -5838,7 +5838,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2713-90-CM26</t>
+          <t>3791-52-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5878,28 +5878,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5019.36</v>
+        <v>2302.17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3791-52-CM26</t>
+          <t>2713-90-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5924,12 +5928,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5939,26 +5943,22 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2302.17</v>
+        <v>5019.36</v>
       </c>
     </row>
     <row r="88">
@@ -6980,7 +6980,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>854-33-CM26</t>
+          <t>854-34-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7020,28 +7020,32 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2134.18</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>854-34-CM26</t>
+          <t>854-33-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7081,26 +7085,22 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2518.75</v>
+        <v>2134.18</v>
       </c>
     </row>
     <row r="106">
@@ -7419,7 +7419,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2500-64-CM26</t>
+          <t>2500-66-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7459,28 +7459,32 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>77.720.988-4</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>941.7</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2500-66-CM26</t>
+          <t>2500-64-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7520,26 +7524,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>803.85</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="113">
@@ -7801,7 +7801,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2500-59-CM26</t>
+          <t>2500-61-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7860,13 +7860,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4703.04</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2500-61-CM26</t>
+          <t>2500-59-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3323.52</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="119">
@@ -8935,7 +8935,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>854-114-CM26</t>
+          <t>854-117-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4231.21</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>854-117-CM26</t>
+          <t>854-114-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>15923.39</v>
+        <v>4231.21</v>
       </c>
     </row>
     <row r="137">
@@ -9313,7 +9313,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>734-485-CM26</t>
+          <t>1274667-259-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9372,13 +9372,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3055.48</v>
+        <v>2907.38</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>734-486-CM26</t>
+          <t>1274667-255-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9418,17 +9418,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1810.43</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1274667-255-CM26</t>
+          <t>734-485-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9468,12 +9468,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9502,13 +9502,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>854.48</v>
+        <v>3055.48</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1274667-259-CM26</t>
+          <t>734-486-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9528,17 +9528,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9548,17 +9548,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2907.38</v>
+        <v>1810.43</v>
       </c>
     </row>
     <row r="145">
@@ -9699,7 +9699,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>967384-2-CM26</t>
+          <t>951405-275-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9739,32 +9739,28 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1390.44</v>
+        <v>2468.03</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>951405-275-CM26</t>
+          <t>967384-2-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9789,7 +9785,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.999.100-1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9804,22 +9800,26 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2468.03</v>
+        <v>1390.44</v>
       </c>
     </row>
     <row r="149">
@@ -10508,7 +10508,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>418-2950-CM26</t>
+          <t>418-2949-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10548,17 +10548,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3802.74</v>
+        <v>3926.29</v>
       </c>
     </row>
     <row r="161">
@@ -10634,7 +10634,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2713-1016-CM26</t>
+          <t>418-2950-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10674,28 +10674,32 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1651.15</v>
+        <v>3802.74</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4778-608-CM26</t>
+          <t>2713-1016-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10710,7 +10714,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10720,12 +10724,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10750,72 +10754,572 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5027.31</v>
+        <v>1651.15</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>4778-608-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>5027.31</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>886182-300-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>1191.35</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>742-92-CM26</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>RED OFFICE SUR LTDA.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>800.54</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3765-861-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>61.307.000-1</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>RED OFFICE SUR LTDA.</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M164" s="2" t="n">
-        <v>800.54</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.602.281-4</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>3937.24</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1403-791-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>847.01</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1057062-464-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>1026.91</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>697209-46-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>2946.54</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1079689-431-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>2809.17</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1079689-445-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>9438.959999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/aysen.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
